--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260731.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>187,515</t>
+          <t>1,241,617</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,241,617</t>
+          <t>187,515</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,886,000</t>
+          <t>5,888,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,888,000</t>
+          <t>1,886,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,650,981</t>
+          <t>2,724,703</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>807,000</t>
+          <t>3,650,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2,724,703</t>
+          <t>807,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,446,384</t>
+          <t>1,244,441</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>152,386</t>
+          <t>1,446,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,244,441</t>
+          <t>152,386</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>11,120,121</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>11,120,121</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,243,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,243,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,203,956</t>
+          <t>814,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>814,000</t>
+          <t>1,636,400</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,636,400</t>
+          <t>5,203,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>238,000</t>
+          <t>401,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>401,000</t>
+          <t>512,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>512,000</t>
+          <t>1,052,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,052,121</t>
+          <t>238,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>333,000</t>
+          <t>68,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>347,000</t>
+          <t>1,844,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>1,844,000</t>
+          <t>333,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>68,538</t>
+          <t>347,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
